--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
   </si>
 </sst>
 </file>
@@ -773,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +812,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920018</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,73 @@
     <t>PERALTA</t>
   </si>
   <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>GALLARDO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>CARLOS</t>
+  </si>
+  <si>
+    <t>ADAHIR</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
   </si>
 </sst>
 </file>
@@ -782,7 +845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -820,10 +883,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -833,6 +896,167 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920201</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920192</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920193</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920202</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920209</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920359</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -79,18 +79,24 @@
     <t>PERALTA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>NEPOMUCENO</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
     <t>CHULIN</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
@@ -103,12 +109,21 @@
     <t>GALLARDO</t>
   </si>
   <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>RICO</t>
   </si>
   <si>
@@ -127,10 +142,19 @@
     <t>CARLOS</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
     <t>ADAHIR</t>
   </si>
   <si>
     <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>YAIR</t>
   </si>
   <si>
     <t>CESAR SAID</t>
@@ -845,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -883,10 +907,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -900,16 +924,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920200</v>
+        <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -923,16 +947,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920201</v>
+        <v>21330051920195</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -946,16 +970,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920192</v>
+        <v>21330051920200</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -964,21 +988,21 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920193</v>
+        <v>21330051920201</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -987,44 +1011,44 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920202</v>
+        <v>20330051920066</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920209</v>
+        <v>21330051920192</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1038,24 +1062,93 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>21330051920193</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920202</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920209</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>20330051920359</v>
       </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
         <v>9</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F12" t="s">
         <v>12</v>
       </c>
-      <c r="G9">
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -79,97 +79,28 @@
     <t>PERALTA</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>NEPOMUCENO</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>BERNABE</t>
   </si>
   <si>
     <t>GALLARDO</t>
   </si>
   <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>CARLOS</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>ADAHIR</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
+    <t>IVAN</t>
   </si>
 </sst>
 </file>
@@ -596,10 +527,10 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>25</v>
@@ -608,7 +539,7 @@
         <v>69.44</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -622,19 +553,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>9</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>64.52</v>
+        <v>70.97</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -687,16 +618,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,16 +644,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>63.89</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -733,16 +670,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -798,16 +738,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>65.63</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -821,16 +761,16 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>69.44</v>
+        <v>63.89</v>
       </c>
       <c r="H3">
         <v>6.7</v>
@@ -847,19 +787,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>64.52</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -907,10 +847,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -924,16 +864,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330061430023</v>
+        <v>21330051920200</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -947,16 +887,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920195</v>
+        <v>21330051920188</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -965,190 +905,6 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920200</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920201</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920066</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920192</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920193</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920202</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920209</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920359</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,31 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>NEPOMUCENO</t>
   </si>
   <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
     <t>ADAHIR</t>
-  </si>
-  <si>
-    <t>IVAN</t>
   </si>
 </sst>
 </file>
@@ -738,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -764,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>63.89</v>
+        <v>86.11</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -790,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>67.73999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -809,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,71 +823,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920018</v>
+        <v>21330051920200</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920200</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920188</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
